--- a/input/Domains/Game/UnitTable.xlsx
+++ b/input/Domains/Game/UnitTable.xlsx
@@ -1,35 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C9A1B7-419F-B344-BE68-3B3BD8961A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1380" yWindow="500" windowWidth="37020" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UNIT_HERO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UNIT_MONSTER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UNIT_HERO" sheetId="1" r:id="rId1"/>
+    <sheet name="UNIT_MONSTER" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+  <si>
+    <t>unitId</t>
+  </si>
+  <si>
+    <t>nameId</t>
+  </si>
+  <si>
+    <t>descId</t>
+  </si>
+  <si>
+    <t>maxHp</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>pk</t>
+  </si>
+  <si>
+    <t>유닛 ID (정본)</t>
+  </si>
+  <si>
+    <t>이름 텍스트 ID</t>
+  </si>
+  <si>
+    <t>설명 텍스트 ID</t>
+  </si>
+  <si>
+    <t>최대 HP</t>
+  </si>
+  <si>
+    <t>hero_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hero_002</t>
+  </si>
+  <si>
+    <t>hero_003</t>
+  </si>
+  <si>
+    <t>hero_004</t>
+  </si>
+  <si>
+    <t>hero_005</t>
+  </si>
+  <si>
+    <t>monster_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster_002</t>
+  </si>
+  <si>
+    <t>monster_003</t>
+  </si>
+  <si>
+    <t>monster_004</t>
+  </si>
+  <si>
+    <t>monster_005</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +129,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,175 +431,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>unitId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nameId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>descId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>pk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>유닛 ID (정본)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>이름 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>설명 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>최대 HP</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>unitId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nameId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>descId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>maxHp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>pk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>유닛 ID (정본)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>이름 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>설명 텍스트 ID</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>최대 HP</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/input/Domains/Game/UnitTable.xlsx
+++ b/input/Domains/Game/UnitTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C9A1B7-419F-B344-BE68-3B3BD8961A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909A6989-257C-C042-A748-682B8746435A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="500" windowWidth="37020" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38560" yWindow="-2200" windowWidth="38080" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT_HERO" sheetId="1" r:id="rId1"/>

--- a/input/Domains/Game/UnitTable.xlsx
+++ b/input/Domains/Game/UnitTable.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909A6989-257C-C042-A748-682B8746435A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F2683B-C901-3347-AA8B-A1BF339E85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38560" yWindow="-2200" windowWidth="38080" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44620" yWindow="-2060" windowWidth="25640" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT_HERO" sheetId="1" r:id="rId1"/>
-    <sheet name="UNIT_MONSTER" sheetId="2" r:id="rId2"/>
+    <sheet name="UNIT_HERO_LEVEL" sheetId="3" r:id="rId2"/>
+    <sheet name="UNIT_MONSTER" sheetId="2" r:id="rId3"/>
+    <sheet name="UNIT_MONSTER_LEVEL" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t>unitId</t>
   </si>
@@ -56,36 +58,62 @@
     <t>최대 HP</t>
   </si>
   <si>
-    <t>hero_001</t>
+    <t>heroType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hero_002</t>
-  </si>
-  <si>
-    <t>hero_003</t>
-  </si>
-  <si>
-    <t>hero_004</t>
-  </si>
-  <si>
-    <t>hero_005</t>
-  </si>
-  <si>
-    <t>monster_001</t>
+    <t>UNIT_HERO_TYPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>monster_002</t>
-  </si>
-  <si>
-    <t>monster_003</t>
-  </si>
-  <si>
-    <t>monster_004</t>
-  </si>
-  <si>
-    <t>monster_005</t>
+    <t>HERO_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HERO_002</t>
+  </si>
+  <si>
+    <t>HERO_003</t>
+  </si>
+  <si>
+    <t>HERO_004</t>
+  </si>
+  <si>
+    <t>HERO_005</t>
+  </si>
+  <si>
+    <t>unit_hero_001</t>
+  </si>
+  <si>
+    <t>unit_hero_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit_hero_002</t>
+  </si>
+  <si>
+    <t>unit_hero_003</t>
+  </si>
+  <si>
+    <t>unit_hero_004</t>
+  </si>
+  <si>
+    <t>unit_hero_005</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unitLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit_monster_001</t>
+  </si>
+  <si>
+    <t>unit_monster_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -432,82 +460,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -517,11 +567,131 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45402A86-376A-5B4F-A1D8-495F727FDD37}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -573,31 +743,131 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{288F280D-250F-B046-AFBF-D446BE65CBC1}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/input/Domains/Game/UnitTable.xlsx
+++ b/input/Domains/Game/UnitTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F2683B-C901-3347-AA8B-A1BF339E85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E340A7D-3C2B-5040-8F2D-79974CB7556E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44620" yWindow="-2060" windowWidth="25640" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6240" yWindow="500" windowWidth="25640" windowHeight="20800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT_HERO" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
   <si>
     <t>unitId</t>
   </si>
@@ -113,6 +113,14 @@
   </si>
   <si>
     <t>unit_monster_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group:true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -480,9 +488,6 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
@@ -496,9 +501,6 @@
       </c>
       <c r="D2" t="s">
         <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -568,115 +570,160 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45402A86-376A-5B4F-A1D8-495F727FDD37}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="C8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>10</v>
       </c>
     </row>
@@ -688,13 +735,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -704,11 +751,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -718,16 +762,13 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -737,11 +778,8 @@
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -754,115 +792,160 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{288F280D-250F-B046-AFBF-D446BE65CBC1}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="C8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>26</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>10</v>
       </c>
     </row>
